--- a/www/flightdata/xlsx/eoss-326.xlsx
+++ b/www/flightdata/xlsx/eoss-326.xlsx
@@ -3411,7 +3411,7 @@
         <v>28033.37</v>
       </c>
       <c r="I2">
-        <v>601</v>
+        <v>432</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
